--- a/product-definitions/spreadsheet/full-troposphere-temperature-profiles.xlsx
+++ b/product-definitions/spreadsheet/full-troposphere-temperature-profiles.xlsx
@@ -308,7 +308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -334,11 +334,6 @@
       <b/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -383,13 +378,13 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -410,22 +405,22 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -2019,7 +2014,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="18" t="s">
         <v>42</v>
@@ -2119,7 +2114,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9"/>
       <c r="B42" s="18" t="s">
         <v>42</v>
@@ -2219,7 +2214,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="9"/>
       <c r="B51" s="18" t="s">
         <v>42</v>
@@ -2295,7 +2290,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9"/>
       <c r="B60" s="18" t="s">
         <v>42</v>
@@ -2368,7 +2363,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="9"/>
       <c r="B69" s="18" t="s">
         <v>42</v>
@@ -2441,7 +2436,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="9"/>
       <c r="B78" s="18" t="s">
         <v>42</v>
@@ -2514,7 +2509,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="9"/>
       <c r="B87" s="18" t="s">
         <v>42</v>
@@ -2587,7 +2582,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="9"/>
       <c r="B96" s="18" t="s">
         <v>42</v>
@@ -2660,7 +2655,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="9"/>
       <c r="B105" s="18" t="s">
         <v>42</v>
@@ -2733,7 +2728,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="9"/>
       <c r="B114" s="18" t="s">
         <v>42</v>
@@ -2806,7 +2801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="9"/>
       <c r="B123" s="18" t="s">
         <v>42</v>
@@ -2879,7 +2874,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="9"/>
       <c r="B132" s="18" t="s">
         <v>42</v>
@@ -2952,7 +2947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="9"/>
       <c r="B141" s="18" t="s">
         <v>42</v>
@@ -3025,7 +3020,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="9"/>
       <c r="B150" s="18" t="s">
         <v>42</v>
@@ -3098,7 +3093,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="9"/>
       <c r="B159" s="18" t="s">
         <v>42</v>
@@ -3171,7 +3166,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="9"/>
       <c r="B168" s="18" t="s">
         <v>42</v>
@@ -3244,7 +3239,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="9"/>
       <c r="B177" s="18" t="s">
         <v>42</v>
@@ -3317,7 +3312,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="9"/>
       <c r="B186" s="18" t="s">
         <v>42</v>
@@ -3390,7 +3385,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="9"/>
       <c r="B195" s="18" t="s">
         <v>42</v>
@@ -3463,7 +3458,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="9"/>
       <c r="B204" s="18" t="s">
         <v>42</v>
